--- a/VerveStacks_NOR_grids_kan50/SysSettings.xlsx
+++ b/VerveStacks_NOR_grids_kan50/SysSettings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_NOR_grids_kan50\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA742704-4CE8-4F16-A9B8-0C90A5BB8EDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BCACB9-3982-4E1B-8189-F5DDB5A4C329}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4012" yWindow="4012" windowWidth="21601" windowHeight="11423" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4096,7 +4096,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D178BC03-723D-49A6-92C2-64A0A49C8855}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FA1B006-3278-4C7A-B1D1-340C7E225C9C}">
   <dimension ref="B3:I45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
@@ -5203,7 +5203,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F30F475-FA20-4C33-81CB-0B57D09E0C56}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F43E639-C3B0-49CD-9FD9-A9C77AFCE6E5}">
   <dimension ref="B3:I45"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <sheetData>
